--- a/data/employees/EMP013/AST-EMP013-06.xlsx
+++ b/data/employees/EMP013/AST-EMP013-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vendor Comparison - Taylor Miller (Procurement)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Taylor Miller | Role: Senior Engineer | Location: Austin | Date: 2025-01-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>83</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>On-Time %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Quality %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Spend YTD ($K)</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acme Components</t>
+          <t>EMP013</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>97</v>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1450</v>
+        <v>67</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GlobalParts Inc</t>
+          <t>EMP013</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mechanical</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91</v>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
-      </c>
-      <c r="F6" t="n">
-        <v>820</v>
+        <v>77</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TechSupply Co</t>
+          <t>EMP013</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>99</v>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2100</v>
+        <v>75</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CleanRoom Solutions</t>
+          <t>EMP013</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumables</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>88</v>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
-      </c>
-      <c r="F8" t="n">
-        <v>340</v>
+        <v>78</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>94</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>75</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>93</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>74</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>73</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>78</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>96</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>94</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>79</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>92</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>69</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>68</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>81</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>67</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>89</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp013 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>64</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP013</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP013 contributes to ast emp013 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>